--- a/data/trans_dic/IP09B01-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP09B01-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado al nivel de asistencia al cole/guardería</t>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado al nivel de asistencia al cole/guardería (tasa de respuesta: 98,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>37,6; 92,2</t>
+          <t>37,76; 91,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31,07; 77,81</t>
+          <t>35,37; 79,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,22; 90,04</t>
+          <t>18,34; 89,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36,98; 100,0</t>
+          <t>40,12; 100,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>56,21; 100,0</t>
+          <t>63,55; 100,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,78; 82,56</t>
+          <t>34,09; 82,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>0,0; 74,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>38,22; 90,19</t>
+          <t>40,13; 89,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>56,62; 89,72</t>
+          <t>57,0; 89,72</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42,01; 73,44</t>
+          <t>41,53; 73,68</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19,63; 77,61</t>
+          <t>19,44; 77,59</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>54,96; 93,59</t>
+          <t>54,47; 92,8</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>47,17; 75,9</t>
+          <t>47,58; 75,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>53,44; 74,96</t>
+          <t>55,1; 75,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39,09; 69,2</t>
+          <t>40,13; 68,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65,01; 86,92</t>
+          <t>64,2; 87,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>51,37; 73,42</t>
+          <t>51,41; 73,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,03; 72,93</t>
+          <t>54,29; 73,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,11; 71,9</t>
+          <t>44,18; 71,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>55,51; 82,61</t>
+          <t>54,76; 81,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>53,19; 70,36</t>
+          <t>52,4; 70,12</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>57,4; 71,65</t>
+          <t>57,21; 71,17</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48,01; 67,46</t>
+          <t>47,37; 66,61</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>62,32; 81,58</t>
+          <t>62,91; 80,86</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>46,39; 86,54</t>
+          <t>47,91; 85,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>47,58; 86,87</t>
+          <t>48,0; 86,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29,51; 76,69</t>
+          <t>27,92; 77,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>45,02; 82,48</t>
+          <t>43,56; 82,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>53,86; 86,32</t>
+          <t>52,41; 86,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,98; 74,72</t>
+          <t>35,08; 74,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,77; 85,14</t>
+          <t>31,57; 85,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>48,9; 88,22</t>
+          <t>48,76; 87,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>57,42; 83,6</t>
+          <t>57,92; 82,67</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>47,19; 73,5</t>
+          <t>46,27; 74,36</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36,89; 70,92</t>
+          <t>39,36; 72,58</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>55,49; 81,58</t>
+          <t>55,02; 81,51</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>54,32; 74,63</t>
+          <t>53,79; 76,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>55,68; 73,21</t>
+          <t>56,49; 73,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42,92; 66,39</t>
+          <t>43,48; 67,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>65,69; 83,67</t>
+          <t>65,19; 84,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>58,47; 75,05</t>
+          <t>58,46; 74,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,12; 70,26</t>
+          <t>52,57; 69,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,52; 68,46</t>
+          <t>44,39; 69,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>59,11; 79,0</t>
+          <t>58,95; 79,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>60,18; 73,77</t>
+          <t>59,94; 73,37</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56,92; 68,92</t>
+          <t>57,16; 69,18</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>47,09; 63,67</t>
+          <t>48,02; 63,87</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>64,47; 79,49</t>
+          <t>65,01; 78,91</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado al nivel de asistencia al cole/guardería (tasa de respuesta: 98,55%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>5258</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7350</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2844</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>8041</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>8862</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>6844</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>7486</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>14119</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>14194</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3488</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>15527</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2952; 7142</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4509; 10097</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>816; 3997</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3764; 9382</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>6588; 10367</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3938; 9546</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2075</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>4377; 9807</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>10366; 16316</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>10091; 17903</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>1404; 5604</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>11052; 18829</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>18502</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>35571</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>17059</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>29125</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>31834</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>42834</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>22763</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>44971</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>50336</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>78405</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>39822</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>74096</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>14133; 22454</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>29895; 41160</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>12471; 21197</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>24124; 32874</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>26449; 37578</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>36472; 49525</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>17017; 27598</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>36044; 53626</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>42525; 56907</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>69477; 86430</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>32968; 46355</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>65039; 83599</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>11991</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10627</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6112</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>10959</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>14213</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>11060</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>5913</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>16065</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>26205</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>21687</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>12025</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>27024</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>8238; 14673</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7315; 13216</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3238; 8933</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>7228; 13656</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>10309; 16987</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>6954; 14737</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>3207; 8643</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>10876; 19456</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>21355; 30480</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>16223; 26071</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>8563; 15791</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>21401; 31704</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>35751</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>53548</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>26016</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>48125</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>54908</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>60738</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>29320</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>68522</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>90659</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>114287</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>55336</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>116648</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>29434; 41587</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>46455; 60424</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>20490; 31947</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>41428; 53707</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>47642; 60804</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>51812; 68059</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>22837; 35626</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>58373; 79100</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>81647; 99940</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>103352; 125068</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>47336; 62952</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>105685; 128287</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP09B01-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP09B01-Estudios-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>37,76; 91,36</t>
+          <t>31,43; 92,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>35,37; 79,22</t>
+          <t>36,5; 79,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,34; 89,84</t>
+          <t>23,6; 90,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40,12; 100,0</t>
+          <t>43,35; 100,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>63,55; 100,0</t>
+          <t>57,48; 100,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,09; 82,64</t>
+          <t>32,43; 81,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 74,83</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>40,13; 89,9</t>
+          <t>38,84; 86,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>57,0; 89,72</t>
+          <t>59,36; 92,41</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41,53; 73,68</t>
+          <t>41,21; 72,41</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19,44; 77,59</t>
+          <t>17,76; 77,05</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>54,47; 92,8</t>
+          <t>53,51; 92,89</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>47,58; 75,6</t>
+          <t>47,38; 76,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>55,1; 75,86</t>
+          <t>55,6; 75,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40,13; 68,21</t>
+          <t>40,23; 71,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64,2; 87,49</t>
+          <t>65,74; 87,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>51,41; 73,03</t>
+          <t>50,32; 72,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,29; 73,72</t>
+          <t>54,0; 73,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,18; 71,66</t>
+          <t>46,18; 71,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>54,76; 81,48</t>
+          <t>56,74; 83,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>52,4; 70,12</t>
+          <t>53,26; 70,7</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>57,21; 71,17</t>
+          <t>57,19; 71,61</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47,37; 66,61</t>
+          <t>47,97; 68,09</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>62,91; 80,86</t>
+          <t>62,75; 81,3</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>47,91; 85,33</t>
+          <t>47,28; 86,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>48,0; 86,72</t>
+          <t>48,85; 86,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27,92; 77,03</t>
+          <t>29,68; 76,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>43,56; 82,3</t>
+          <t>43,71; 83,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>52,41; 86,36</t>
+          <t>54,31; 86,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,08; 74,35</t>
+          <t>35,84; 73,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,57; 85,08</t>
+          <t>31,81; 79,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>48,76; 87,23</t>
+          <t>48,26; 87,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>57,92; 82,67</t>
+          <t>56,88; 81,52</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>46,27; 74,36</t>
+          <t>47,81; 73,82</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39,36; 72,58</t>
+          <t>36,79; 73,36</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>55,02; 81,51</t>
+          <t>54,47; 81,56</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>53,79; 76,0</t>
+          <t>54,79; 75,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>56,49; 73,47</t>
+          <t>56,48; 72,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43,48; 67,8</t>
+          <t>43,74; 66,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>65,19; 84,51</t>
+          <t>65,62; 84,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>58,46; 74,61</t>
+          <t>59,33; 75,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,57; 69,06</t>
+          <t>53,37; 69,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,39; 69,25</t>
+          <t>46,18; 68,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>58,95; 79,88</t>
+          <t>58,71; 79,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>59,94; 73,37</t>
+          <t>60,06; 72,94</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57,16; 69,18</t>
+          <t>57,1; 68,75</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48,02; 63,87</t>
+          <t>48,12; 64,71</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>65,01; 78,91</t>
+          <t>65,01; 80,01</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2952; 7142</t>
+          <t>2457; 7216</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4509; 10097</t>
+          <t>4653; 10089</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>816; 3997</t>
+          <t>1050; 4018</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3764; 9382</t>
+          <t>4067; 9382</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6588; 10367</t>
+          <t>5958; 10367</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3938; 9546</t>
+          <t>3746; 9435</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 2075</t>
+          <t>0; 2773</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4377; 9807</t>
+          <t>4236; 9469</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10366; 16316</t>
+          <t>10795; 16804</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10091; 17903</t>
+          <t>10012; 17594</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1404; 5604</t>
+          <t>1283; 5565</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11052; 18829</t>
+          <t>10858; 18847</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14133; 22454</t>
+          <t>14074; 22755</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29895; 41160</t>
+          <t>30164; 40872</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12471; 21197</t>
+          <t>12502; 22066</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24124; 32874</t>
+          <t>24702; 32757</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26449; 37578</t>
+          <t>25890; 37081</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36472; 49525</t>
+          <t>36280; 49280</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17017; 27598</t>
+          <t>17787; 27400</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>36044; 53626</t>
+          <t>37344; 54912</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>42525; 56907</t>
+          <t>43227; 57376</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>69477; 86430</t>
+          <t>69449; 86964</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32968; 46355</t>
+          <t>33382; 47382</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>65039; 83599</t>
+          <t>64881; 84052</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8238; 14673</t>
+          <t>8130; 14898</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7315; 13216</t>
+          <t>7445; 13256</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3238; 8933</t>
+          <t>3442; 8885</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7228; 13656</t>
+          <t>7253; 13802</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10309; 16987</t>
+          <t>10682; 16971</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6954; 14737</t>
+          <t>7104; 14624</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3207; 8643</t>
+          <t>3232; 8108</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10876; 19456</t>
+          <t>10764; 19405</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>21355; 30480</t>
+          <t>20969; 30056</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16223; 26071</t>
+          <t>16764; 25883</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8563; 15791</t>
+          <t>8005; 15960</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>21401; 31704</t>
+          <t>21189; 31724</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>29434; 41587</t>
+          <t>29982; 41303</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>46455; 60424</t>
+          <t>46450; 59996</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20490; 31947</t>
+          <t>20610; 31256</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>41428; 53707</t>
+          <t>41701; 53764</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>47642; 60804</t>
+          <t>48345; 61351</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>51812; 68059</t>
+          <t>52596; 68499</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22837; 35626</t>
+          <t>23760; 35233</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>58373; 79100</t>
+          <t>58136; 79103</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>81647; 99940</t>
+          <t>81807; 99351</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>103352; 125068</t>
+          <t>103227; 124300</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>47336; 62952</t>
+          <t>47433; 63783</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>105685; 128287</t>
+          <t>105698; 130081</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP09B01-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP09B01-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>85,48%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>59,25%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>23,23%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>71,22%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>67,25%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>57,66%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>63,92%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>85,71%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>85,48%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>59,25%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>23,23%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>71,05%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>31,43; 92,29</t>
+          <t>56,21; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>36,5; 79,15</t>
+          <t>33,78; 82,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,6; 90,32</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43,35; 100,0</t>
+          <t>41,11; 90,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>57,48; 100,0</t>
+          <t>37,6; 92,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,43; 81,68</t>
+          <t>31,07; 77,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>20,22; 90,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>38,84; 86,81</t>
+          <t>23,94; 100,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>59,36; 92,41</t>
+          <t>56,62; 89,72</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41,21; 72,41</t>
+          <t>42,01; 73,44</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17,76; 77,05</t>
+          <t>19,63; 77,61</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>53,51; 92,89</t>
+          <t>49,84; 88,31</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>61,87%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>63,76%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>59,1%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>67,68%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>62,29%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>65,56%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>54,89%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>77,52%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>61,87%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>63,76%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>59,1%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>71,34%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>47,38; 76,61</t>
+          <t>51,37; 73,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>55,6; 75,33</t>
+          <t>54,03; 72,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40,23; 71,0</t>
+          <t>46,11; 71,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65,74; 87,18</t>
+          <t>54,63; 81,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>50,32; 72,07</t>
+          <t>47,17; 75,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,0; 73,35</t>
+          <t>53,44; 74,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,18; 71,14</t>
+          <t>39,09; 69,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>56,74; 83,43</t>
+          <t>64,39; 86,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>53,26; 70,7</t>
+          <t>53,19; 70,36</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>57,19; 71,61</t>
+          <t>57,4; 71,65</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47,97; 68,09</t>
+          <t>48,01; 67,46</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>62,75; 81,3</t>
+          <t>61,99; 80,54</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>72,26%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>55,8%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>58,2%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>76,54%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>69,73%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>69,73%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>52,71%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>66,05%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>72,26%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>55,8%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>58,2%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>71,0%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>47,28; 86,63</t>
+          <t>53,86; 86,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>48,85; 86,98</t>
+          <t>35,98; 74,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29,68; 76,62</t>
+          <t>32,77; 85,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>43,71; 83,18</t>
+          <t>55,31; 90,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>54,31; 86,28</t>
+          <t>46,39; 86,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,84; 73,78</t>
+          <t>47,58; 86,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,81; 79,81</t>
+          <t>29,51; 76,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>48,26; 87,0</t>
+          <t>44,23; 81,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>56,88; 81,52</t>
+          <t>57,42; 83,6</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>47,81; 73,82</t>
+          <t>47,19; 73,5</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36,79; 73,36</t>
+          <t>36,89; 70,92</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>54,47; 81,56</t>
+          <t>58,2; 82,37</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>67,38%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>61,63%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>56,99%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>70,03%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>65,34%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>65,11%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>55,21%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>75,73%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>67,38%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>61,63%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>56,99%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>71,23%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>54,79; 75,48</t>
+          <t>58,47; 75,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>56,48; 72,95</t>
+          <t>54,12; 70,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43,74; 66,33</t>
+          <t>45,52; 68,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>65,62; 84,6</t>
+          <t>60,48; 79,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>59,33; 75,29</t>
+          <t>54,32; 74,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,37; 69,5</t>
+          <t>55,68; 73,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,18; 68,48</t>
+          <t>42,92; 66,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>58,71; 79,88</t>
+          <t>63,28; 81,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>60,06; 72,94</t>
+          <t>60,18; 73,77</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57,1; 68,75</t>
+          <t>56,92; 68,92</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48,12; 64,71</t>
+          <t>47,09; 63,67</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>65,01; 80,01</t>
+          <t>64,01; 78,34</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>8862</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6844</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>6883</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>5258</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>7350</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>2844</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>8041</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>8862</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>6844</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7486</t>
+          <t>3097</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15527</t>
+          <t>9981</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2457; 7216</t>
+          <t>5827; 10367</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4653; 10089</t>
+          <t>3902; 9536</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1050; 4018</t>
+          <t>0; 2773</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4067; 9382</t>
+          <t>3973; 8773</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5958; 10367</t>
+          <t>2940; 7208</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3746; 9435</t>
+          <t>3960; 9917</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 2773</t>
+          <t>900; 4006</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4236; 9469</t>
+          <t>1049; 4383</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10795; 16804</t>
+          <t>10297; 16315</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10012; 17594</t>
+          <t>10207; 17844</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1283; 5565</t>
+          <t>1417; 5605</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10858; 18847</t>
+          <t>7002; 12406</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>43</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>31834</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>42834</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>22763</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>40219</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>18502</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>35571</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>17059</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>29125</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>31834</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>42834</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>22763</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>44971</t>
+          <t>28917</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>74096</t>
+          <t>69135</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14074; 22755</t>
+          <t>26429; 37777</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30164; 40872</t>
+          <t>36298; 48995</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12502; 22066</t>
+          <t>17759; 27691</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24702; 32757</t>
+          <t>32466; 48274</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>25890; 37081</t>
+          <t>14012; 22544</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36280; 49280</t>
+          <t>28995; 40668</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17787; 27400</t>
+          <t>12148; 21506</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>37344; 54912</t>
+          <t>24136; 32455</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>43227; 57376</t>
+          <t>43169; 57104</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>69449; 86964</t>
+          <t>69707; 87016</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33382; 47382</t>
+          <t>33413; 46944</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>64881; 84052</t>
+          <t>60078; 78058</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>14213</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>11060</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5913</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>15139</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>11991</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>10627</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>6112</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>10959</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>14213</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>11060</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>5913</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16065</t>
+          <t>11125</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>27024</t>
+          <t>26265</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8130; 14898</t>
+          <t>10594; 16980</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7445; 13256</t>
+          <t>7131; 14810</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3442; 8885</t>
+          <t>3329; 8649</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7253; 13802</t>
+          <t>10939; 17840</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10682; 16971</t>
+          <t>7977; 14882</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7104; 14624</t>
+          <t>7251; 13240</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3232; 8108</t>
+          <t>3422; 8893</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10764; 19405</t>
+          <t>7613; 14072</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>20969; 30056</t>
+          <t>21168; 30821</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16764; 25883</t>
+          <t>16546; 25771</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8005; 15960</t>
+          <t>8025; 15430</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>21189; 31724</t>
+          <t>21529; 30472</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>77</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>64</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>54908</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>60738</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>29320</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>62241</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>35751</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>53548</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>26016</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>48125</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>54908</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>60738</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>29320</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>68522</t>
+          <t>43139</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>116648</t>
+          <t>105380</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>29982; 41303</t>
+          <t>47648; 61161</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>46450; 59996</t>
+          <t>53340; 69245</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20610; 31256</t>
+          <t>23419; 35223</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>41701; 53764</t>
+          <t>53751; 70273</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>48345; 61351</t>
+          <t>29720; 40835</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>52596; 68499</t>
+          <t>45792; 60211</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23760; 35233</t>
+          <t>20224; 31287</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>58136; 79103</t>
+          <t>37389; 48108</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>81807; 99351</t>
+          <t>81973; 100480</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>103227; 124300</t>
+          <t>102905; 124602</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>47433; 63783</t>
+          <t>46415; 62759</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>105698; 130081</t>
+          <t>94707; 115901</t>
         </is>
       </c>
     </row>
